--- a/batchstudent/Result/anlpvhe187047/TC6/GradeDetail.xlsx
+++ b/batchstudent/Result/anlpvhe187047/TC6/GradeDetail.xlsx
@@ -164,10 +164,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -176,12 +176,6 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -210,18 +204,6 @@
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -248,7 +230,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -257,17 +239,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -290,7 +262,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -300,14 +272,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -317,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -984,11 +942,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R35"/>
+  <x:dimension ref="A1:R23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1095,25 +1053,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>49</x:v>
@@ -1151,7 +1109,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1171,8 +1129,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1192,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1207,7 +1165,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,8 +1185,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R4" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1248,13 +1206,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>46</x:v>
@@ -1263,7 +1221,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,8 +1241,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R5" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1304,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1319,7 +1277,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1339,8 +1297,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R6" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1360,13 +1318,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>47</x:v>
@@ -1375,7 +1333,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1395,8 +1353,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1416,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1431,7 +1389,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1451,8 +1409,8 @@
       <x:c r="Q8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R8" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1472,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1487,7 +1445,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1507,8 +1465,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R9" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1528,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1543,7 +1501,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1563,8 +1521,8 @@
       <x:c r="Q10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R10" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1584,10 +1542,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1599,7 +1557,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1619,8 +1577,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R11" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1640,10 +1598,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1655,7 +1613,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1675,8 +1633,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R12" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1711,25 +1669,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0">
-        <x:v>35204</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>49</x:v>
@@ -1767,7 +1725,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
         <x:v>17</x:v>
@@ -1787,8 +1745,8 @@
       <x:c r="Q14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R14" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1808,10 +1766,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1823,7 +1781,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
         <x:v>17</x:v>
@@ -1843,8 +1801,8 @@
       <x:c r="Q15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R15" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R15" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
@@ -1864,13 +1822,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1879,7 +1837,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
         <x:v>17</x:v>
@@ -1899,8 +1857,8 @@
       <x:c r="Q16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R16" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R16" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1920,10 +1878,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1935,7 +1893,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
         <x:v>17</x:v>
@@ -1955,8 +1913,8 @@
       <x:c r="Q17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R17" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1976,13 +1934,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -1991,7 +1949,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -2011,8 +1969,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R18" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2032,10 +1990,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -2047,7 +2005,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
         <x:v>17</x:v>
@@ -2067,8 +2025,8 @@
       <x:c r="Q19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R19" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2088,10 +2046,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2103,7 +2061,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
         <x:v>17</x:v>
@@ -2123,8 +2081,8 @@
       <x:c r="Q20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R20" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2144,10 +2102,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2159,7 +2117,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
         <x:v>17</x:v>
@@ -2179,8 +2137,8 @@
       <x:c r="Q21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R21" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R21" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2200,10 +2158,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2215,7 +2173,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>17</x:v>
@@ -2235,8 +2193,8 @@
       <x:c r="Q22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="R22" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2256,10 +2214,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
@@ -2271,7 +2229,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2291,680 +2249,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:18">
-      <x:c r="A24" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L24" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M24" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P24" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q24" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:18">
-      <x:c r="A25" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L25" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M25" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P25" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="Q25" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R25" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:18">
-      <x:c r="A26" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M26" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P26" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q26" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="R26" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:18">
-      <x:c r="A27" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M27" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P27" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="Q27" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R27" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:18">
-      <x:c r="A28" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K28" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L28" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M28" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N28" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O28" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P28" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q28" s="0">
-        <x:v>48182</x:v>
-      </x:c>
-      <x:c r="R28" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:18">
-      <x:c r="A29" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K29" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L29" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M29" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N29" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O29" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P29" s="0">
-        <x:v>60698</x:v>
-      </x:c>
-      <x:c r="Q29" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R29" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:18">
-      <x:c r="A30" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K30" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L30" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M30" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N30" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O30" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P30" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q30" s="0">
-        <x:v>60698</x:v>
-      </x:c>
-      <x:c r="R30" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:18">
-      <x:c r="A31" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K31" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L31" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M31" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N31" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O31" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P31" s="0">
-        <x:v>55520</x:v>
-      </x:c>
-      <x:c r="Q31" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R31" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:18">
-      <x:c r="A32" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L32" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M32" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N32" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O32" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P32" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q32" s="0">
-        <x:v>55520</x:v>
-      </x:c>
-      <x:c r="R32" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:18">
-      <x:c r="A33" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K33" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L33" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M33" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N33" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O33" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P33" s="0">
-        <x:v>54078</x:v>
-      </x:c>
-      <x:c r="Q33" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R33" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:18">
-      <x:c r="A34" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K34" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L34" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M34" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N34" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O34" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P34" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q34" s="0">
-        <x:v>54078</x:v>
-      </x:c>
-      <x:c r="R34" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:18">
-      <x:c r="A35" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L35" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M35" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N35" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P35" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q35" s="0">
-        <x:v>35204</x:v>
-      </x:c>
-      <x:c r="R35" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="R23" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
